--- a/paper/tables/data_real_count_by_dataset.xlsx
+++ b/paper/tables/data_real_count_by_dataset.xlsx
@@ -5,17 +5,30 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Clustering-Validity\results\count\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Clustering-Validity\paper\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1E3DC1D6-6923-46B5-866E-EE9116550464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B5D295-024F-49EA-B594-40470CCC65EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C42F7130-91EA-465A-9CCF-4DDAC21057BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C42F7130-91EA-465A-9CCF-4DDAC21057BC}"/>
   </bookViews>
   <sheets>
     <sheet name="data_real_count_by_dataset" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1022,9 +1035,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ADF763-0621-4318-B13F-E6B13797413A}">
   <dimension ref="A1:T38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1127,17 +1140,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1149,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1161,19 +1174,19 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K4">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="L4">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M4">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="N4">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="O4">
         <v>92</v>
@@ -1182,23 +1195,23 @@
         <v>101</v>
       </c>
       <c r="Q4">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="S4">
         <f>SUM(B4:I4)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <f>SUM(J4:Q4)</f>
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1222,19 +1235,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="K5">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="L5">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="M5">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="N5">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="O5">
         <v>90</v>
@@ -1243,18 +1256,18 @@
         <v>125</v>
       </c>
       <c r="Q5">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="S5">
         <f t="shared" ref="S5:S38" si="0">SUM(B5:I5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <f t="shared" ref="T5:T38" si="1">SUM(J5:Q5)</f>
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1283,19 +1296,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="K6">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="L6">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N6">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="O6">
         <v>64</v>
@@ -1304,7 +1317,7 @@
         <v>149</v>
       </c>
       <c r="Q6">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
@@ -1312,10 +1325,10 @@
       </c>
       <c r="T6">
         <f t="shared" si="1"/>
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1341,22 +1354,22 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K7">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="N7">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="O7">
         <v>68</v>
@@ -1365,23 +1378,23 @@
         <v>78</v>
       </c>
       <c r="Q7">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <f t="shared" si="1"/>
-        <v>967</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1393,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1405,19 +1418,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="K8">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L8">
+        <v>145</v>
+      </c>
+      <c r="M8">
+        <v>134</v>
+      </c>
+      <c r="N8">
         <v>148</v>
-      </c>
-      <c r="M8">
-        <v>137</v>
-      </c>
-      <c r="N8">
-        <v>252</v>
       </c>
       <c r="O8">
         <v>98</v>
@@ -1426,18 +1439,18 @@
         <v>143</v>
       </c>
       <c r="Q8">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <f t="shared" si="1"/>
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1454,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1466,19 +1479,19 @@
         <v>2</v>
       </c>
       <c r="J9">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="K9">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L9">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M9">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="N9">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="O9">
         <v>43</v>
@@ -1491,19 +1504,19 @@
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <f t="shared" si="1"/>
-        <v>794</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1524,22 +1537,22 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="K10">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="L10">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M10">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N10">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="O10">
         <v>85</v>
@@ -1548,18 +1561,18 @@
         <v>112</v>
       </c>
       <c r="Q10">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="S10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <f t="shared" si="1"/>
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1567,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1585,22 +1598,22 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="K11">
+        <v>147</v>
+      </c>
+      <c r="L11">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>6</v>
+      </c>
+      <c r="N11">
         <v>154</v>
-      </c>
-      <c r="L11">
-        <v>38</v>
-      </c>
-      <c r="M11">
-        <v>4</v>
-      </c>
-      <c r="N11">
-        <v>82</v>
       </c>
       <c r="O11">
         <v>82</v>
@@ -1609,7 +1622,7 @@
         <v>119</v>
       </c>
       <c r="Q11">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
@@ -1617,15 +1630,15 @@
       </c>
       <c r="T11">
         <f t="shared" si="1"/>
-        <v>742</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1637,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1649,19 +1662,19 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K12">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="L12">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M12">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N12">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="O12">
         <v>69</v>
@@ -1670,18 +1683,18 @@
         <v>143</v>
       </c>
       <c r="Q12">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="S12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <f t="shared" si="1"/>
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1689,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1710,19 +1723,19 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="K13">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="L13">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M13">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N13">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="O13">
         <v>96</v>
@@ -1731,18 +1744,18 @@
         <v>142</v>
       </c>
       <c r="Q13">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="S13">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <f t="shared" si="1"/>
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1750,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1768,22 +1781,22 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="K14">
         <v>198</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N14">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="O14">
         <v>125</v>
@@ -1792,18 +1805,18 @@
         <v>115</v>
       </c>
       <c r="Q14">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <f t="shared" si="1"/>
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1811,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1829,22 +1842,22 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K15">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="L15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="O15">
         <v>72</v>
@@ -1853,7 +1866,7 @@
         <v>126</v>
       </c>
       <c r="Q15">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="S15">
         <f t="shared" si="0"/>
@@ -1861,21 +1874,21 @@
       </c>
       <c r="T15">
         <f t="shared" si="1"/>
-        <v>834</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1890,22 +1903,22 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="K16">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L16">
         <v>135</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N16">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="O16">
         <v>90</v>
@@ -1914,7 +1927,7 @@
         <v>150</v>
       </c>
       <c r="Q16">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="S16">
         <f t="shared" si="0"/>
@@ -1922,15 +1935,15 @@
       </c>
       <c r="T16">
         <f t="shared" si="1"/>
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1942,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1954,19 +1967,19 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="K17">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="L17">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M17">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N17">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="O17">
         <v>93</v>
@@ -1975,18 +1988,18 @@
         <v>145</v>
       </c>
       <c r="Q17">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="S17">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T17">
         <f t="shared" si="1"/>
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2012,22 +2025,22 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="K18">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="L18">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M18">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N18">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="O18">
         <v>113</v>
@@ -2036,18 +2049,18 @@
         <v>89</v>
       </c>
       <c r="Q18">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="S18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <f t="shared" si="1"/>
-        <v>951</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2064,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -2073,22 +2086,22 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K19">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L19">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M19">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="N19">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="O19">
         <v>77</v>
@@ -2097,26 +2110,26 @@
         <v>95</v>
       </c>
       <c r="Q19">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="S19">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <f t="shared" si="1"/>
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2134,22 +2147,22 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K20">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="L20">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M20">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N20">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="O20">
         <v>104</v>
@@ -2158,18 +2171,18 @@
         <v>44</v>
       </c>
       <c r="Q20">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="S20">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <f t="shared" si="1"/>
-        <v>809</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2177,16 +2190,16 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2195,22 +2208,22 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="K21">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="L21">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M21">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N21">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="O21">
         <v>95</v>
@@ -2219,18 +2232,18 @@
         <v>95</v>
       </c>
       <c r="Q21">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="S21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T21">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2238,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2247,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2256,22 +2269,22 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="K22">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="L22">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M22">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N22">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O22">
         <v>57</v>
@@ -2280,18 +2293,18 @@
         <v>106</v>
       </c>
       <c r="Q22">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="S22">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T22">
         <f t="shared" si="1"/>
-        <v>745</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2308,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2320,19 +2333,19 @@
         <v>2</v>
       </c>
       <c r="J23">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K23">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="L23">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M23">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="N23">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="O23">
         <v>74</v>
@@ -2341,18 +2354,18 @@
         <v>26</v>
       </c>
       <c r="Q23">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="S23">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <f t="shared" si="1"/>
-        <v>760</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2360,16 +2373,16 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -2381,19 +2394,19 @@
         <v>2</v>
       </c>
       <c r="J24">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="K24">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="L24">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="M24">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="N24">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="O24">
         <v>68</v>
@@ -2402,35 +2415,35 @@
         <v>87</v>
       </c>
       <c r="Q24">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="S24">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T24">
         <f t="shared" si="1"/>
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2439,22 +2452,22 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="K25">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L25">
         <v>115</v>
       </c>
       <c r="M25">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="N25">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="O25">
         <v>51</v>
@@ -2463,18 +2476,18 @@
         <v>121</v>
       </c>
       <c r="Q25">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="S25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <f t="shared" si="1"/>
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2482,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -2500,22 +2513,22 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K26">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="L26">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M26">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="N26">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="O26">
         <v>79</v>
@@ -2524,18 +2537,18 @@
         <v>86</v>
       </c>
       <c r="Q26">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="S26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <f t="shared" si="1"/>
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2543,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2564,44 +2577,44 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K27">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="L27">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="M27">
-        <v>13</v>
+        <v>161</v>
       </c>
       <c r="N27">
-        <v>131</v>
+        <v>269</v>
       </c>
       <c r="O27">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="P27">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="Q27">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="S27">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <f t="shared" si="1"/>
-        <v>930</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2622,22 +2635,22 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="K28">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="L28">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M28">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N28">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="O28">
         <v>67</v>
@@ -2646,7 +2659,7 @@
         <v>122</v>
       </c>
       <c r="Q28">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="S28">
         <f t="shared" si="0"/>
@@ -2654,18 +2667,18 @@
       </c>
       <c r="T28">
         <f t="shared" si="1"/>
-        <v>994</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2683,22 +2696,22 @@
         <v>3</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K29">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="L29">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M29">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N29">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="O29">
         <v>90</v>
@@ -2707,35 +2720,35 @@
         <v>11</v>
       </c>
       <c r="Q29">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="S29">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <f t="shared" si="1"/>
-        <v>749</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -2744,22 +2757,22 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K30">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="L30">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M30">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="N30">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="O30">
         <v>69</v>
@@ -2768,18 +2781,18 @@
         <v>94</v>
       </c>
       <c r="Q30">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="S30">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <f t="shared" si="1"/>
-        <v>989</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2796,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2805,22 +2818,22 @@
         <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="K31">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="L31">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M31">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N31">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="O31">
         <v>41</v>
@@ -2829,7 +2842,7 @@
         <v>35</v>
       </c>
       <c r="Q31">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S31">
         <f t="shared" si="0"/>
@@ -2837,10 +2850,10 @@
       </c>
       <c r="T31">
         <f t="shared" si="1"/>
-        <v>501</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2901,7 +2914,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2962,7 +2975,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -3023,7 +3036,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -3034,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>2</v>
@@ -3049,19 +3062,19 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K35">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L35">
         <v>87</v>
       </c>
       <c r="M35">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N35">
         <v>164</v>
@@ -3073,7 +3086,7 @@
         <v>115</v>
       </c>
       <c r="Q35">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="S35">
         <f t="shared" si="0"/>
@@ -3081,27 +3094,27 @@
       </c>
       <c r="T35">
         <f t="shared" si="1"/>
-        <v>972</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3110,22 +3123,22 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="K36">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="L36">
         <v>103</v>
       </c>
       <c r="M36">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N36">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="O36">
         <v>56</v>
@@ -3134,18 +3147,18 @@
         <v>127</v>
       </c>
       <c r="Q36">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="S36">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <f t="shared" si="1"/>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3162,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -3171,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K37">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L37">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N37">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="O37">
         <v>35</v>
@@ -3195,18 +3208,18 @@
         <v>104</v>
       </c>
       <c r="Q37">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S37">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <f t="shared" si="1"/>
-        <v>698</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -3214,10 +3227,10 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3232,22 +3245,22 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="K38">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="L38">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M38">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="N38">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="O38">
         <v>63</v>
@@ -3256,18 +3269,19 @@
         <v>71</v>
       </c>
       <c r="Q38">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="S38">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <f t="shared" si="1"/>
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>